--- a/data/trans_camb/P32C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,55</t>
+          <t>-2,36; 7,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,2</t>
+          <t>-4,01; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -1,33</t>
+          <t>-8,55; -1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,89</t>
+          <t>-5,04; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,01</t>
+          <t>-3,98; 3,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 0,0</t>
+          <t>-6,77; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 4,78</t>
+          <t>-2,22; 4,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,74</t>
+          <t>-2,84; 3,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -1,29</t>
+          <t>-6,75; -1,25</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,88; 451,44</t>
+          <t>-42,43; 511,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 354,8</t>
+          <t>-69,72; 325,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,94; 353,07</t>
+          <t>-52,68; 347,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 303,08</t>
+          <t>-62,13; 312,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,03</t>
+          <t>-3,98; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,06</t>
+          <t>-2,78; 3,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,95</t>
+          <t>-5,4; -0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,61</t>
+          <t>-3,06; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,25</t>
+          <t>-2,34; 2,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,7</t>
+          <t>-4,12; -0,72</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 129,99</t>
+          <t>-88,65; 134,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 320,66</t>
+          <t>-70,05; 323,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 97,18</t>
+          <t>-87,72; 118,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 293,37</t>
+          <t>-72,94; 241,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,44; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,87</t>
+          <t>-0,98; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,62</t>
+          <t>-0,21; 3,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,76</t>
+          <t>-0,42; 1,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,96</t>
+          <t>0,27; 2,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,73</t>
+          <t>-3,47; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; -1,01</t>
+          <t>-5,86; -1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,13</t>
+          <t>-4,33; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,0</t>
+          <t>-5,18; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,0</t>
+          <t>-5,0; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,08</t>
+          <t>-4,3; 1,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,76</t>
+          <t>-2,68; 1,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,79</t>
+          <t>-4,2; -0,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,63</t>
+          <t>-3,39; 0,63</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 416,33</t>
+          <t>-88,39; 322,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 214,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,31; 262,57</t>
+          <t>-87,78; 233,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-94,35; 71,61</t>
+          <t>-90,01; 91,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,02</t>
+          <t>-1,15; 5,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,0</t>
+          <t>-5,08; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 0,0</t>
+          <t>-16,65; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 0,0</t>
+          <t>-16,8; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 19,33</t>
+          <t>-7,1; 19,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,2</t>
+          <t>-3,72; 2,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,0</t>
+          <t>-5,7; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,29</t>
+          <t>-4,1; 2,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,4</t>
+          <t>-2,0; 1,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,19</t>
+          <t>-2,4; 1,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,26</t>
+          <t>-1,41; 3,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,0</t>
+          <t>-4,3; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,0</t>
+          <t>-4,31; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,54</t>
+          <t>-1,28; 4,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,51</t>
+          <t>-2,17; 0,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,69</t>
+          <t>-2,21; 0,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,86</t>
+          <t>-0,8; 2,89</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-72,81; 779,12</t>
+          <t>-65,11; 792,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,81</t>
+          <t>-2,7; 1,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,19</t>
+          <t>-2,57; 2,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,27</t>
+          <t>-2,76; 2,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,35</t>
+          <t>-1,92; 1,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,46</t>
+          <t>-1,81; 1,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,77</t>
+          <t>-2,24; 1,71</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,03; 165,1</t>
+          <t>-68,54; 181,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 177,79</t>
+          <t>-67,24; 213,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 289,7</t>
+          <t>-73,26; 227,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 197,27</t>
+          <t>-68,96; 192,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 187,9</t>
+          <t>-65,05; 203,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 185,16</t>
+          <t>-73,65; 184,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,09</t>
+          <t>-1,24; 2,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,97</t>
+          <t>-1,9; 0,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,07</t>
+          <t>-1,8; 1,25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,95</t>
+          <t>-2,57; 0,68</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,32</t>
+          <t>-2,14; 1,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -0,42</t>
+          <t>-3,39; -0,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,4</t>
+          <t>-1,25; 1,42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,66</t>
+          <t>-1,74; 0,59</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,65</t>
+          <t>-1,78; 0,59</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 252,69</t>
+          <t>-67,69; 318,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 188,99</t>
+          <t>-87,58; 114,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,59</t>
+          <t>-100,0; 211,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-66,58; 217,1</t>
+          <t>-68,65; 163,45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 106,18</t>
+          <t>-81,29; 88,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-92,21; 150,89</t>
+          <t>-100,0; 95,56</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,01</t>
+          <t>-0,75; 0,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,55</t>
+          <t>-1,16; 0,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,01</t>
+          <t>-1,47; 0,05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,03</t>
+          <t>-1,47; 0,04</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,37</t>
+          <t>-1,35; 0,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,92</t>
+          <t>-1,13; 0,96</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,51</t>
+          <t>-0,85; 0,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,27</t>
+          <t>-0,96; 0,29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,09</t>
+          <t>-1,13; 0,14</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 69,46</t>
+          <t>-32,57; 62,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 37,29</t>
+          <t>-49,54; 39,03</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 4,48</t>
+          <t>-62,75; 6,17</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,9</t>
+          <t>-100,0; 49,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 132,08</t>
+          <t>-85,98; 110,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 193,9</t>
+          <t>-71,93; 211,17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 41,85</t>
+          <t>-44,43; 40,66</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 25,16</t>
+          <t>-48,67; 26,0</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 9,12</t>
+          <t>-59,32; 11,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,72</t>
+          <t>-2,3; 7,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,05</t>
+          <t>-4,58; 5,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,31</t>
+          <t>-9,01; -1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,86</t>
+          <t>-5,38; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,88</t>
+          <t>-4,02; 3,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,0</t>
+          <t>-8,0; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,73</t>
+          <t>-1,84; 5,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,74</t>
+          <t>-2,9; 3,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -1,25</t>
+          <t>-6,56; -1,24</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 511,19</t>
+          <t>-44,59; 470,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,72; 325,47</t>
+          <t>-75,49; 313,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 347,71</t>
+          <t>-49,02; 350,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 312,18</t>
+          <t>-67,07; 241,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,23</t>
+          <t>-3,94; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,23</t>
+          <t>-2,66; 3,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,91</t>
+          <t>-5,75; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,8</t>
+          <t>-3,02; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,22</t>
+          <t>-2,08; 2,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; -0,72</t>
+          <t>-4,11; -0,68</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-88,65; 134,84</t>
+          <t>-87,77; 165,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 323,22</t>
+          <t>-72,42; 277,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,72; 118,97</t>
+          <t>-89,59; 129,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 241,57</t>
+          <t>-69,94; 287,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,72</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,0</t>
+          <t>-2,62; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,9</t>
+          <t>-0,99; 2,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,85</t>
+          <t>0,24; 4,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,99</t>
+          <t>-0,69; 1,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,97</t>
+          <t>0,44; 3,42</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335,89%</t>
+          <t>408,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>438,56%</t>
+          <t>514,93%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,59</t>
+          <t>-3,25; 2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -1,02</t>
+          <t>-5,8; -0,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,13</t>
+          <t>-4,31; 0,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,0</t>
+          <t>-5,6; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,0</t>
+          <t>-5,49; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,16</t>
+          <t>-4,16; 1,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,67</t>
+          <t>-2,7; 1,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,79</t>
+          <t>-4,24; -0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,63</t>
+          <t>-3,23; 0,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-47,67%</t>
+          <t>-53,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-34,83%</t>
+          <t>-36,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,73%</t>
+          <t>-51,12%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,39; 322,28</t>
+          <t>-83,46; 379,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 160,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 233,29</t>
+          <t>-85,62; 276,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 91,36</t>
+          <t>-89,15; 102,74</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,49</t>
+          <t>-1,18; 6,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 0,0</t>
+          <t>-14,77; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 0,0</t>
+          <t>-16,3; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 19,18</t>
+          <t>-7,01; 14,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,67</t>
+          <t>-3,47; 2,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,0</t>
+          <t>-6,51; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,46</t>
+          <t>-4,6; 2,19</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-37,45%</t>
+          <t>-41,06%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,25</t>
+          <t>-2,02; 1,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,1</t>
+          <t>-2,08; 1,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,37</t>
+          <t>-1,42; 2,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,0</t>
+          <t>-4,58; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,0</t>
+          <t>-4,58; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,81</t>
+          <t>-1,85; 4,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,52</t>
+          <t>-1,93; 0,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,41</t>
+          <t>-1,98; 0,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,89</t>
+          <t>-0,6; 3,19</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>149,93%</t>
+          <t>147,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>108,85%</t>
+          <t>104,56%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 792,39</t>
+          <t>-60,79; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,94</t>
+          <t>-2,67; 1,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,22</t>
+          <t>-2,43; 2,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,26</t>
+          <t>-3,1; 1,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,73; 7,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,38</t>
+          <t>-1,82; 1,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,48</t>
+          <t>-1,88; 1,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,71</t>
+          <t>-1,35; 2,66</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-8,72%</t>
+          <t>-18,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-3,25%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 181,0</t>
+          <t>-72,35; 169,23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,24; 213,03</t>
+          <t>-67,72; 234,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 227,88</t>
+          <t>-79,41; 164,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 192,0</t>
+          <t>-67,99; 166,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 203,55</t>
+          <t>-70,18; 194,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 184,1</t>
+          <t>-57,28; 302,12</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,24</t>
+          <t>-1,17; 2,31</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,85</t>
+          <t>-1,78; 0,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,25</t>
+          <t>-1,82; 1,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,68</t>
+          <t>-2,55; 0,95</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,32</t>
+          <t>-2,51; 1,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,39; -0,42</t>
+          <t>-3,45; -0,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,42</t>
+          <t>-1,31; 1,18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,59</t>
+          <t>-1,73; 0,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,59</t>
+          <t>-1,76; 0,54</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-31,18%</t>
+          <t>-31,94%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-47,68%</t>
+          <t>-48,48%</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 318,7</t>
+          <t>-66,43; 324,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-87,58; 114,24</t>
+          <t>-86,38; 132,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,93</t>
+          <t>-100,0; 208,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 163,45</t>
+          <t>-73,44; 143,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-81,29; 88,76</t>
+          <t>-82,37; 108,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,56</t>
+          <t>-100,0; 128,71</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,95</t>
+          <t>-0,73; 1,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,55</t>
+          <t>-1,13; 0,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,05</t>
+          <t>-1,46; 0,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,04</t>
+          <t>-1,48; 0,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,37</t>
+          <t>-1,37; 0,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,96</t>
+          <t>-0,75; 1,56</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,49</t>
+          <t>-0,83; 0,47</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,29</t>
+          <t>-0,94; 0,28</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,14</t>
+          <t>-0,96; 0,32</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-36,48%</t>
+          <t>-36,92%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-1,52%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-31,23%</t>
+          <t>-22,24%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 62,72</t>
+          <t>-32,44; 67,96</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 39,03</t>
+          <t>-48,39; 39,83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-62,75; 6,17</t>
+          <t>-62,97; 4,23</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,34</t>
+          <t>-100,0; 37,17</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 110,65</t>
+          <t>-86,14; 107,51</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 211,17</t>
+          <t>-60,57; 346,45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 40,66</t>
+          <t>-43,18; 36,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 26,0</t>
+          <t>-51,12; 23,35</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 11,59</t>
+          <t>-50,44; 26,15</t>
         </is>
       </c>
     </row>
